--- a/artfynd/A 64837-2023 artfynd.xlsx
+++ b/artfynd/A 64837-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134456772</v>
+        <v>135330529</v>
       </c>
       <c r="B3" t="n">
-        <v>79452</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>864</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623724</v>
+        <v>623697</v>
       </c>
       <c r="R3" t="n">
-        <v>7310158</v>
+        <v>7310241</v>
       </c>
       <c r="S3" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,22 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,44 +877,48 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134456771</v>
+        <v>135330532</v>
       </c>
       <c r="B4" t="n">
-        <v>91988</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1204</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +928,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623825</v>
+        <v>623736</v>
       </c>
       <c r="R4" t="n">
-        <v>7310297</v>
+        <v>7310280</v>
       </c>
       <c r="S4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,22 +958,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,22 +988,26 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134456774</v>
+        <v>134456772</v>
       </c>
       <c r="B5" t="n">
-        <v>83222</v>
+        <v>79452</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1015,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,13 +1039,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623732</v>
+        <v>623724</v>
       </c>
       <c r="R5" t="n">
-        <v>7310148</v>
+        <v>7310158</v>
       </c>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1066,7 +1074,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1084,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,32 +1111,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134456780</v>
+        <v>134456771</v>
       </c>
       <c r="B6" t="n">
-        <v>83222</v>
+        <v>91988</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,13 +1146,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623770</v>
+        <v>623825</v>
       </c>
       <c r="R6" t="n">
-        <v>7310054</v>
+        <v>7310297</v>
       </c>
       <c r="S6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,7 +1181,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1191,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134456779</v>
+        <v>134456774</v>
       </c>
       <c r="B7" t="n">
-        <v>79130</v>
+        <v>83222</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1229,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,13 +1253,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623810</v>
+        <v>623732</v>
       </c>
       <c r="R7" t="n">
-        <v>7310162</v>
+        <v>7310148</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1280,7 +1288,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1298,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1325,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134456769</v>
+        <v>134456780</v>
       </c>
       <c r="B8" t="n">
-        <v>79992</v>
+        <v>83222</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1336,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1360,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623900</v>
+        <v>623770</v>
       </c>
       <c r="R8" t="n">
-        <v>7310143</v>
+        <v>7310054</v>
       </c>
       <c r="S8" t="n">
         <v>14</v>
@@ -1387,7 +1395,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1405,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1432,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134456776</v>
+        <v>135333617</v>
       </c>
       <c r="B9" t="n">
-        <v>79992</v>
+        <v>83222</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,21 +1443,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,13 +1467,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623807</v>
+        <v>623762</v>
       </c>
       <c r="R9" t="n">
-        <v>7310160</v>
+        <v>7310114</v>
       </c>
       <c r="S9" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1489,22 +1497,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1519,22 +1527,26 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134456777</v>
+        <v>135333622</v>
       </c>
       <c r="B10" t="n">
-        <v>79992</v>
+        <v>83222</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1554,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,13 +1578,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>623758</v>
+        <v>623739</v>
       </c>
       <c r="R10" t="n">
-        <v>7310258</v>
+        <v>7310146</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1596,22 +1608,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1626,44 +1638,48 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134456770</v>
+        <v>135330534</v>
       </c>
       <c r="B11" t="n">
-        <v>78377</v>
+        <v>91937</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6487</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,13 +1689,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>623875</v>
+        <v>623725</v>
       </c>
       <c r="R11" t="n">
-        <v>7310171</v>
+        <v>7310245</v>
       </c>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1703,22 +1719,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>20:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>20:37</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1733,44 +1749,48 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134456773</v>
+        <v>135333620</v>
       </c>
       <c r="B12" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,13 +1800,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>623744</v>
+        <v>623771</v>
       </c>
       <c r="R12" t="n">
-        <v>7310162</v>
+        <v>7310137</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1810,27 +1830,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:20</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack i tall.</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1845,22 +1860,26 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134456775</v>
+        <v>135333618</v>
       </c>
       <c r="B13" t="n">
-        <v>57975</v>
+        <v>78776</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1868,21 +1887,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,13 +1911,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>623790</v>
+        <v>623772</v>
       </c>
       <c r="R13" t="n">
-        <v>7310142</v>
+        <v>7310131</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1922,27 +1941,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Gamla hackmärken i tall</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1957,22 +1971,26 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134456766</v>
+        <v>135333623</v>
       </c>
       <c r="B14" t="n">
-        <v>79963</v>
+        <v>78776</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,21 +1998,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2004,13 +2022,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>623830</v>
+        <v>623707</v>
       </c>
       <c r="R14" t="n">
-        <v>7310041</v>
+        <v>7310261</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2034,22 +2052,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2064,22 +2082,26 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134456767</v>
+        <v>135333630</v>
       </c>
       <c r="B15" t="n">
-        <v>79963</v>
+        <v>78776</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2087,21 +2109,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2111,13 +2133,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>623900</v>
+        <v>623777</v>
       </c>
       <c r="R15" t="n">
-        <v>7310120</v>
+        <v>7310269</v>
       </c>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2141,22 +2163,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2171,22 +2193,26 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134456778</v>
+        <v>134456779</v>
       </c>
       <c r="B16" t="n">
-        <v>79396</v>
+        <v>79130</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2194,21 +2220,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>260591</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2218,13 +2244,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>623793</v>
+        <v>623810</v>
       </c>
       <c r="R16" t="n">
-        <v>7310206</v>
+        <v>7310162</v>
       </c>
       <c r="S16" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2253,7 +2279,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2263,7 +2289,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2287,6 +2313,2422 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135333627</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>623753</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7310291</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>134456769</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>623900</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7310143</v>
+      </c>
+      <c r="S18" t="n">
+        <v>14</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>134456776</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>623807</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7310160</v>
+      </c>
+      <c r="S19" t="n">
+        <v>18</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>134456777</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>623758</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7310258</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135330531</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>623713</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7310247</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135333621</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>623770</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7310168</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135333625</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>623754</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7310291</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135333631</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>623776</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7310265</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135333633</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>623803</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7310251</v>
+      </c>
+      <c r="S25" t="n">
+        <v>20</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135333636</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>623860</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7310128</v>
+      </c>
+      <c r="S26" t="n">
+        <v>6</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>134456770</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78377</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>623875</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7310171</v>
+      </c>
+      <c r="S27" t="n">
+        <v>11</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135333628</v>
+      </c>
+      <c r="B28" t="n">
+        <v>78377</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>623755</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7310283</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>134456773</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>623744</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7310162</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack i tall.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>134456775</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>623790</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7310142</v>
+      </c>
+      <c r="S30" t="n">
+        <v>20</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Gamla hackmärken i tall</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135330530</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>623714</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7310251</v>
+      </c>
+      <c r="S31" t="n">
+        <v>9</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135333626</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>623753</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7310291</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>134456766</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>623830</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7310041</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>134456767</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>623900</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7310120</v>
+      </c>
+      <c r="S34" t="n">
+        <v>13</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135333624</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>623709</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7310261</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135333629</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>623753</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7310283</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>134456778</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>623793</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7310206</v>
+      </c>
+      <c r="S37" t="n">
+        <v>11</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135330533</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>623740</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7310280</v>
+      </c>
+      <c r="S38" t="n">
+        <v>17</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 64837-2023 artfynd.xlsx
+++ b/artfynd/A 64837-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1004,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134456772</v>
+        <v>135336962</v>
       </c>
       <c r="B5" t="n">
-        <v>79452</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,21 +1015,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>864</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,13 +1039,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623724</v>
+        <v>623775</v>
       </c>
       <c r="R5" t="n">
-        <v>7310158</v>
+        <v>7310254</v>
       </c>
       <c r="S5" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1069,22 +1069,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,44 +1099,48 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134456771</v>
+        <v>134456772</v>
       </c>
       <c r="B6" t="n">
-        <v>91988</v>
+        <v>79452</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1146,13 +1150,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623825</v>
+        <v>623724</v>
       </c>
       <c r="R6" t="n">
-        <v>7310297</v>
+        <v>7310158</v>
       </c>
       <c r="S6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1181,7 +1185,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1191,7 +1195,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,10 +1222,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134456774</v>
+        <v>135336961</v>
       </c>
       <c r="B7" t="n">
-        <v>83222</v>
+        <v>81355</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1229,21 +1233,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>1049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1253,13 +1257,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623732</v>
+        <v>623755</v>
       </c>
       <c r="R7" t="n">
-        <v>7310148</v>
+        <v>7310257</v>
       </c>
       <c r="S7" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1283,22 +1287,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1313,44 +1317,48 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134456780</v>
+        <v>134456771</v>
       </c>
       <c r="B8" t="n">
-        <v>83222</v>
+        <v>91988</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1360,13 +1368,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623770</v>
+        <v>623825</v>
       </c>
       <c r="R8" t="n">
-        <v>7310054</v>
+        <v>7310297</v>
       </c>
       <c r="S8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1395,7 +1403,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1405,7 +1413,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,7 +1440,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135333617</v>
+        <v>134456774</v>
       </c>
       <c r="B9" t="n">
         <v>83222</v>
@@ -1467,13 +1475,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623762</v>
+        <v>623732</v>
       </c>
       <c r="R9" t="n">
-        <v>7310114</v>
+        <v>7310148</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1497,22 +1505,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1527,23 +1535,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135333622</v>
+        <v>134456780</v>
       </c>
       <c r="B10" t="n">
         <v>83222</v>
@@ -1578,13 +1582,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>623739</v>
+        <v>623770</v>
       </c>
       <c r="R10" t="n">
-        <v>7310146</v>
+        <v>7310054</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1608,22 +1612,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,48 +1642,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135330534</v>
+        <v>135333617</v>
       </c>
       <c r="B11" t="n">
-        <v>91937</v>
+        <v>83222</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1689,13 +1689,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>623725</v>
+        <v>623762</v>
       </c>
       <c r="R11" t="n">
-        <v>7310245</v>
+        <v>7310114</v>
       </c>
       <c r="S11" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>20:37</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>20:37</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1749,12 +1749,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1765,32 +1765,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135333620</v>
+        <v>135333622</v>
       </c>
       <c r="B12" t="n">
-        <v>79373</v>
+        <v>83222</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1800,13 +1800,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>623771</v>
+        <v>623739</v>
       </c>
       <c r="R12" t="n">
-        <v>7310137</v>
+        <v>7310146</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1876,32 +1876,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135333618</v>
+        <v>135330534</v>
       </c>
       <c r="B13" t="n">
-        <v>78776</v>
+        <v>91937</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6437</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>623772</v>
+        <v>623725</v>
       </c>
       <c r="R13" t="n">
-        <v>7310131</v>
+        <v>7310245</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>20:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>20:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1971,12 +1971,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1987,45 +1987,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135333623</v>
+        <v>135331260</v>
       </c>
       <c r="B14" t="n">
-        <v>78776</v>
+        <v>79373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Myrås, Pi lm</t>
+          <t>Myrås, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>623707</v>
+        <v>623814</v>
       </c>
       <c r="R14" t="n">
-        <v>7310261</v>
+        <v>7310091</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2057,7 +2057,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2082,12 +2082,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2098,45 +2098,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135333630</v>
+        <v>135331261</v>
       </c>
       <c r="B15" t="n">
-        <v>78776</v>
+        <v>79373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Myrås, Pi lm</t>
+          <t>Myrås, Pi lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>623777</v>
+        <v>623779</v>
       </c>
       <c r="R15" t="n">
-        <v>7310269</v>
+        <v>7310157</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2193,12 +2193,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2209,32 +2209,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134456779</v>
+        <v>135333620</v>
       </c>
       <c r="B16" t="n">
-        <v>79130</v>
+        <v>79373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2244,13 +2244,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>623810</v>
+        <v>623771</v>
       </c>
       <c r="R16" t="n">
-        <v>7310162</v>
+        <v>7310137</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2274,22 +2274,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2304,22 +2304,26 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135333627</v>
+        <v>135333618</v>
       </c>
       <c r="B17" t="n">
-        <v>79130</v>
+        <v>78776</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2327,21 +2331,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2351,10 +2355,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>623753</v>
+        <v>623772</v>
       </c>
       <c r="R17" t="n">
-        <v>7310291</v>
+        <v>7310131</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2386,7 +2390,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2396,7 +2400,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2427,10 +2431,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134456769</v>
+        <v>135333623</v>
       </c>
       <c r="B18" t="n">
-        <v>79992</v>
+        <v>78776</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2438,21 +2442,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2462,13 +2466,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>623900</v>
+        <v>623707</v>
       </c>
       <c r="R18" t="n">
-        <v>7310143</v>
+        <v>7310261</v>
       </c>
       <c r="S18" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2492,22 +2496,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2522,22 +2526,26 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134456776</v>
+        <v>135333630</v>
       </c>
       <c r="B19" t="n">
-        <v>79992</v>
+        <v>78776</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2545,21 +2553,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2569,13 +2577,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>623807</v>
+        <v>623777</v>
       </c>
       <c r="R19" t="n">
-        <v>7310160</v>
+        <v>7310269</v>
       </c>
       <c r="S19" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2599,22 +2607,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2629,22 +2637,26 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134456777</v>
+        <v>135336952</v>
       </c>
       <c r="B20" t="n">
-        <v>79992</v>
+        <v>78776</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2652,21 +2664,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2676,13 +2688,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>623758</v>
+        <v>623805</v>
       </c>
       <c r="R20" t="n">
-        <v>7310258</v>
+        <v>7310020</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2706,22 +2718,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2736,22 +2748,26 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135330531</v>
+        <v>134456779</v>
       </c>
       <c r="B21" t="n">
-        <v>79992</v>
+        <v>79130</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2759,21 +2775,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2783,13 +2799,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>623713</v>
+        <v>623810</v>
       </c>
       <c r="R21" t="n">
-        <v>7310247</v>
+        <v>7310162</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2813,22 +2829,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2843,26 +2859,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135333621</v>
+        <v>135333627</v>
       </c>
       <c r="B22" t="n">
-        <v>79992</v>
+        <v>79130</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2870,21 +2882,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2894,10 +2906,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>623770</v>
+        <v>623753</v>
       </c>
       <c r="R22" t="n">
-        <v>7310168</v>
+        <v>7310291</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2929,7 +2941,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2939,7 +2951,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2970,7 +2982,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135333625</v>
+        <v>134456769</v>
       </c>
       <c r="B23" t="n">
         <v>79992</v>
@@ -3005,13 +3017,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>623754</v>
+        <v>623900</v>
       </c>
       <c r="R23" t="n">
-        <v>7310291</v>
+        <v>7310143</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3035,22 +3047,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3065,23 +3077,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135333631</v>
+        <v>134456776</v>
       </c>
       <c r="B24" t="n">
         <v>79992</v>
@@ -3116,13 +3124,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>623776</v>
+        <v>623807</v>
       </c>
       <c r="R24" t="n">
-        <v>7310265</v>
+        <v>7310160</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3146,22 +3154,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3176,23 +3184,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135333633</v>
+        <v>134456777</v>
       </c>
       <c r="B25" t="n">
         <v>79992</v>
@@ -3227,10 +3231,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>623803</v>
+        <v>623758</v>
       </c>
       <c r="R25" t="n">
-        <v>7310251</v>
+        <v>7310258</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3257,22 +3261,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3287,23 +3291,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135333636</v>
+        <v>135330531</v>
       </c>
       <c r="B26" t="n">
         <v>79992</v>
@@ -3338,13 +3338,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>623860</v>
+        <v>623713</v>
       </c>
       <c r="R26" t="n">
-        <v>7310128</v>
+        <v>7310247</v>
       </c>
       <c r="S26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3398,12 +3398,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3414,10 +3414,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134456770</v>
+        <v>135333621</v>
       </c>
       <c r="B27" t="n">
-        <v>78377</v>
+        <v>79992</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3425,21 +3425,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3449,13 +3449,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>623875</v>
+        <v>623770</v>
       </c>
       <c r="R27" t="n">
-        <v>7310171</v>
+        <v>7310168</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3479,22 +3479,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3509,22 +3509,26 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135333628</v>
+        <v>135333625</v>
       </c>
       <c r="B28" t="n">
-        <v>78377</v>
+        <v>79992</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3532,21 +3536,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3556,10 +3560,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>623755</v>
+        <v>623754</v>
       </c>
       <c r="R28" t="n">
-        <v>7310283</v>
+        <v>7310291</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3591,7 +3595,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3601,7 +3605,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3632,10 +3636,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134456773</v>
+        <v>135333631</v>
       </c>
       <c r="B29" t="n">
-        <v>57975</v>
+        <v>79992</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3643,21 +3647,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3667,10 +3671,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>623744</v>
+        <v>623776</v>
       </c>
       <c r="R29" t="n">
-        <v>7310162</v>
+        <v>7310265</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3697,27 +3701,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:20</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack i tall.</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3732,22 +3731,26 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134456775</v>
+        <v>135333633</v>
       </c>
       <c r="B30" t="n">
-        <v>57975</v>
+        <v>79992</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3755,21 +3758,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3779,10 +3782,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>623790</v>
+        <v>623803</v>
       </c>
       <c r="R30" t="n">
-        <v>7310142</v>
+        <v>7310251</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3809,27 +3812,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Gamla hackmärken i tall</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3844,22 +3842,26 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135330530</v>
+        <v>135333636</v>
       </c>
       <c r="B31" t="n">
-        <v>79131</v>
+        <v>79992</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3867,21 +3869,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3891,13 +3893,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>623714</v>
+        <v>623860</v>
       </c>
       <c r="R31" t="n">
-        <v>7310251</v>
+        <v>7310128</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3926,7 +3928,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3936,7 +3938,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3951,12 +3953,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Petya Valcheva</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3967,10 +3969,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135333626</v>
+        <v>135336953</v>
       </c>
       <c r="B32" t="n">
-        <v>79131</v>
+        <v>79992</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3978,21 +3980,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4002,13 +4004,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>623753</v>
+        <v>623790</v>
       </c>
       <c r="R32" t="n">
-        <v>7310291</v>
+        <v>7310126</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4037,7 +4039,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4047,7 +4049,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4062,12 +4064,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4078,10 +4080,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134456766</v>
+        <v>135336958</v>
       </c>
       <c r="B33" t="n">
-        <v>79963</v>
+        <v>79992</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4089,21 +4091,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4113,13 +4115,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>623830</v>
+        <v>623711</v>
       </c>
       <c r="R33" t="n">
-        <v>7310041</v>
+        <v>7310252</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4143,22 +4145,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4173,22 +4175,26 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134456767</v>
+        <v>135336963</v>
       </c>
       <c r="B34" t="n">
-        <v>79963</v>
+        <v>79992</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4196,21 +4202,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4220,13 +4226,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>623900</v>
+        <v>623802</v>
       </c>
       <c r="R34" t="n">
-        <v>7310120</v>
+        <v>7310245</v>
       </c>
       <c r="S34" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4250,22 +4256,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4280,22 +4286,26 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135333624</v>
+        <v>135358159</v>
       </c>
       <c r="B35" t="n">
-        <v>79963</v>
+        <v>79992</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4303,34 +4313,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Myrås, Pi lm</t>
+          <t>Myrås, Pi lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>623709</v>
+        <v>623777</v>
       </c>
       <c r="R35" t="n">
-        <v>7310261</v>
+        <v>7310175</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4362,7 +4372,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4372,7 +4382,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4387,12 +4397,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4403,10 +4413,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135333629</v>
+        <v>134456770</v>
       </c>
       <c r="B36" t="n">
-        <v>79963</v>
+        <v>78377</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4414,21 +4424,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4438,13 +4448,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>623753</v>
+        <v>623875</v>
       </c>
       <c r="R36" t="n">
-        <v>7310283</v>
+        <v>7310171</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4468,22 +4478,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4498,26 +4508,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134456778</v>
+        <v>135333628</v>
       </c>
       <c r="B37" t="n">
-        <v>79396</v>
+        <v>78377</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4525,21 +4531,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>260591</v>
+        <v>6487</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4549,13 +4555,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>623793</v>
+        <v>623755</v>
       </c>
       <c r="R37" t="n">
-        <v>7310206</v>
+        <v>7310283</v>
       </c>
       <c r="S37" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4579,22 +4585,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4609,22 +4615,26 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135330533</v>
+        <v>134456773</v>
       </c>
       <c r="B38" t="n">
-        <v>79396</v>
+        <v>57975</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4632,21 +4642,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>260591</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4656,13 +4666,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>623740</v>
+        <v>623744</v>
       </c>
       <c r="R38" t="n">
-        <v>7310280</v>
+        <v>7310162</v>
       </c>
       <c r="S38" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4686,22 +4696,27 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack i tall.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4716,15 +4731,2245 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>134456775</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>623790</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7310142</v>
+      </c>
+      <c r="S39" t="n">
+        <v>20</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Gamla hackmärken i tall</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135336954</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>623782</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7310156</v>
+      </c>
+      <c r="S40" t="n">
+        <v>7</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135336955</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>623750</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7310194</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135336960</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>623741</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7310258</v>
+      </c>
+      <c r="S42" t="n">
+        <v>8</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135336965</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>623813</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7310236</v>
+      </c>
+      <c r="S43" t="n">
+        <v>6</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135331264</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>623755</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7310300</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Maja Rancic</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Maja Rancic</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135336951</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>623787</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7310002</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135330530</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>623714</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7310251</v>
+      </c>
+      <c r="S46" t="n">
+        <v>9</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
           <t>Petya Valcheva</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
+      <c r="AX46" t="inlineStr">
         <is>
           <t>Petya Valcheva</t>
         </is>
       </c>
-      <c r="AY38" t="inlineStr">
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135333626</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>623753</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7310291</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>134456766</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>623830</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7310041</v>
+      </c>
+      <c r="S48" t="n">
+        <v>25</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>134456767</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>623900</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7310120</v>
+      </c>
+      <c r="S49" t="n">
+        <v>13</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>135331263</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>623731</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7310280</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Maja Rancic</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Maja Rancic</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>135333624</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>623709</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7310261</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>135333629</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>623753</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7310283</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>135336957</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>623699</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7310215</v>
+      </c>
+      <c r="S53" t="n">
+        <v>8</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>134456778</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>623793</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7310206</v>
+      </c>
+      <c r="S54" t="n">
+        <v>11</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>135330533</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>623740</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7310280</v>
+      </c>
+      <c r="S55" t="n">
+        <v>17</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135336956</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>623738</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7310208</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135336959</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>623723</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7310256</v>
+      </c>
+      <c r="S57" t="n">
+        <v>9</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>135336964</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>623808</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7310244</v>
+      </c>
+      <c r="S58" t="n">
+        <v>9</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>rikligt med soral</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>

--- a/artfynd/A 64837-2023 artfynd.xlsx
+++ b/artfynd/A 64837-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY58"/>
+  <dimension ref="A1:AZ58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456768</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330529</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330532</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336962</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1219,6 +1244,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456772</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1330,6 +1360,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336961</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1437,6 +1472,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456771</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1544,6 +1584,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456774</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1651,6 +1696,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456780</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1762,6 +1812,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333617</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1873,6 +1928,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333622</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1984,6 +2044,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330534</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2095,6 +2160,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331260</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2206,6 +2276,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331261</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2317,6 +2392,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333620</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2428,6 +2508,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333618</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2539,6 +2624,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333623</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2650,6 +2740,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333630</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2761,6 +2856,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336952</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2868,6 +2968,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456779</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2979,6 +3084,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333627</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3086,6 +3196,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456769</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3193,6 +3308,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456776</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3300,6 +3420,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456777</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3411,6 +3536,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330531</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3522,6 +3652,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333621</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3633,6 +3768,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333625</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3744,6 +3884,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333631</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3855,6 +4000,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333633</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3966,6 +4116,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333636</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4077,6 +4232,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336953</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4188,6 +4348,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336958</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4299,6 +4464,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336963</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4410,6 +4580,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358159</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4517,6 +4692,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456770</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4628,6 +4808,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333628</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4740,6 +4925,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456773</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4852,6 +5042,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456775</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4968,6 +5163,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336954</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5084,6 +5284,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336955</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5200,6 +5405,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336960</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5316,6 +5526,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336965</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5427,6 +5642,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331264</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5538,6 +5758,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336951</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5649,6 +5874,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330530</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5760,6 +5990,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333626</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5867,6 +6102,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456766</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5974,6 +6214,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456767</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6085,6 +6330,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331263</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6196,6 +6446,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333624</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6307,6 +6562,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333629</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6418,6 +6678,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336957</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6525,6 +6790,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456778</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6636,6 +6906,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330533</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6747,6 +7022,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336956</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6858,6 +7138,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336959</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6974,8 +7259,72 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336964</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 64837-2023 artfynd.xlsx
+++ b/artfynd/A 64837-2023 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135330529</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>135330532</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>135336962</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>135336961</v>
       </c>
       <c r="B7" t="n">
-        <v>81355</v>
+        <v>81393</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>135333617</v>
       </c>
       <c r="B11" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>135333622</v>
       </c>
       <c r="B12" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>135330534</v>
       </c>
       <c r="B13" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>135331260</v>
       </c>
       <c r="B14" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>135331261</v>
       </c>
       <c r="B15" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>135333620</v>
       </c>
       <c r="B16" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>135333618</v>
       </c>
       <c r="B17" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>135333623</v>
       </c>
       <c r="B18" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>135333630</v>
       </c>
       <c r="B19" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>135336952</v>
       </c>
       <c r="B20" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>135333627</v>
       </c>
       <c r="B22" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>135330531</v>
       </c>
       <c r="B26" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>135333621</v>
       </c>
       <c r="B27" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>135333625</v>
       </c>
       <c r="B28" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>135333631</v>
       </c>
       <c r="B29" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>135333633</v>
       </c>
       <c r="B30" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>135333636</v>
       </c>
       <c r="B31" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>135336953</v>
       </c>
       <c r="B32" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>135336958</v>
       </c>
       <c r="B33" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>135336963</v>
       </c>
       <c r="B34" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         <v>135358159</v>
       </c>
       <c r="B35" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>135333628</v>
       </c>
       <c r="B37" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>135336954</v>
       </c>
       <c r="B40" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>135336955</v>
       </c>
       <c r="B41" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>135336960</v>
       </c>
       <c r="B42" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5416,7 +5416,7 @@
         <v>135336965</v>
       </c>
       <c r="B43" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>135331264</v>
       </c>
       <c r="B44" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
         <v>135336951</v>
       </c>
       <c r="B45" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v>135330530</v>
       </c>
       <c r="B46" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>135333626</v>
       </c>
       <c r="B47" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>135331263</v>
       </c>
       <c r="B50" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>135333624</v>
       </c>
       <c r="B51" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         <v>135333629</v>
       </c>
       <c r="B52" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>135336957</v>
       </c>
       <c r="B53" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         <v>135330533</v>
       </c>
       <c r="B55" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>135336956</v>
       </c>
       <c r="B56" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7033,7 +7033,7 @@
         <v>135336959</v>
       </c>
       <c r="B57" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7149,7 +7149,7 @@
         <v>135336964</v>
       </c>
       <c r="B58" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 64837-2023 artfynd.xlsx
+++ b/artfynd/A 64837-2023 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135330529</v>
       </c>
       <c r="B3" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>135330532</v>
       </c>
       <c r="B4" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>135336962</v>
       </c>
       <c r="B5" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>135336961</v>
       </c>
       <c r="B7" t="n">
-        <v>81393</v>
+        <v>81420</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>135333617</v>
       </c>
       <c r="B11" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>135333622</v>
       </c>
       <c r="B12" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>135330534</v>
       </c>
       <c r="B13" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>135331260</v>
       </c>
       <c r="B14" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>135331261</v>
       </c>
       <c r="B15" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>135333620</v>
       </c>
       <c r="B16" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>135333618</v>
       </c>
       <c r="B17" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>135333623</v>
       </c>
       <c r="B18" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>135333630</v>
       </c>
       <c r="B19" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>135336952</v>
       </c>
       <c r="B20" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>135333627</v>
       </c>
       <c r="B22" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>135330531</v>
       </c>
       <c r="B26" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>135333621</v>
       </c>
       <c r="B27" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>135333625</v>
       </c>
       <c r="B28" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>135333631</v>
       </c>
       <c r="B29" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>135333633</v>
       </c>
       <c r="B30" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>135333636</v>
       </c>
       <c r="B31" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>135336953</v>
       </c>
       <c r="B32" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>135336958</v>
       </c>
       <c r="B33" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>135336963</v>
       </c>
       <c r="B34" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         <v>135358159</v>
       </c>
       <c r="B35" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>135333628</v>
       </c>
       <c r="B37" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>135331264</v>
       </c>
       <c r="B44" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
         <v>135336951</v>
       </c>
       <c r="B45" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v>135330530</v>
       </c>
       <c r="B46" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>135333626</v>
       </c>
       <c r="B47" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>135331263</v>
       </c>
       <c r="B50" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>135333624</v>
       </c>
       <c r="B51" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         <v>135333629</v>
       </c>
       <c r="B52" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>135336957</v>
       </c>
       <c r="B53" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         <v>135330533</v>
       </c>
       <c r="B55" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>135336956</v>
       </c>
       <c r="B56" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7033,7 +7033,7 @@
         <v>135336959</v>
       </c>
       <c r="B57" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7149,7 +7149,7 @@
         <v>135336964</v>
       </c>
       <c r="B58" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 64837-2023 artfynd.xlsx
+++ b/artfynd/A 64837-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ16"/>
+  <dimension ref="A1:AZ58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134456772</v>
+        <v>135330529</v>
       </c>
       <c r="B3" t="n">
-        <v>79452</v>
+        <v>79107</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>864</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623724</v>
+        <v>623697</v>
       </c>
       <c r="R3" t="n">
-        <v>7310158</v>
+        <v>7310241</v>
       </c>
       <c r="S3" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,49 +887,53 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134456772</t>
+          <t>https://artportalen.se/Sighting/135330529</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134456771</v>
+        <v>135330532</v>
       </c>
       <c r="B4" t="n">
-        <v>91988</v>
+        <v>79107</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1204</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,13 +943,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623825</v>
+        <v>623736</v>
       </c>
       <c r="R4" t="n">
-        <v>7310297</v>
+        <v>7310280</v>
       </c>
       <c r="S4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +973,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,27 +1003,31 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134456771</t>
+          <t>https://artportalen.se/Sighting/135330532</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134456774</v>
+        <v>135336962</v>
       </c>
       <c r="B5" t="n">
-        <v>83222</v>
+        <v>79107</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +1035,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,13 +1059,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623732</v>
+        <v>623775</v>
       </c>
       <c r="R5" t="n">
-        <v>7310148</v>
+        <v>7310254</v>
       </c>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,22 +1089,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,27 +1119,31 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134456774</t>
+          <t>https://artportalen.se/Sighting/135336962</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134456780</v>
+        <v>134456772</v>
       </c>
       <c r="B6" t="n">
-        <v>83222</v>
+        <v>79452</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,21 +1151,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,13 +1175,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623770</v>
+        <v>623724</v>
       </c>
       <c r="R6" t="n">
-        <v>7310054</v>
+        <v>7310158</v>
       </c>
       <c r="S6" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,7 +1210,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1220,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,16 +1246,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134456780</t>
+          <t>https://artportalen.se/Sighting/134456772</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134456779</v>
+        <v>135336961</v>
       </c>
       <c r="B7" t="n">
-        <v>79130</v>
+        <v>81423</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1263,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>1049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,13 +1287,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623810</v>
+        <v>623755</v>
       </c>
       <c r="R7" t="n">
-        <v>7310162</v>
+        <v>7310257</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,22 +1317,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,49 +1347,53 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134456779</t>
+          <t>https://artportalen.se/Sighting/135336961</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134456769</v>
+        <v>134456771</v>
       </c>
       <c r="B8" t="n">
-        <v>79992</v>
+        <v>91988</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,13 +1403,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623900</v>
+        <v>623825</v>
       </c>
       <c r="R8" t="n">
-        <v>7310143</v>
+        <v>7310297</v>
       </c>
       <c r="S8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1422,7 +1438,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1448,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,16 +1474,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134456769</t>
+          <t>https://artportalen.se/Sighting/134456771</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134456776</v>
+        <v>134456774</v>
       </c>
       <c r="B9" t="n">
-        <v>79992</v>
+        <v>83222</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,21 +1491,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,13 +1515,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623807</v>
+        <v>623732</v>
       </c>
       <c r="R9" t="n">
-        <v>7310160</v>
+        <v>7310148</v>
       </c>
       <c r="S9" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1534,7 +1550,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1560,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1570,16 +1586,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134456776</t>
+          <t>https://artportalen.se/Sighting/134456774</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134456777</v>
+        <v>134456780</v>
       </c>
       <c r="B10" t="n">
-        <v>79992</v>
+        <v>83222</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,21 +1603,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,13 +1627,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>623758</v>
+        <v>623770</v>
       </c>
       <c r="R10" t="n">
-        <v>7310258</v>
+        <v>7310054</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1646,7 +1662,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1672,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1682,16 +1698,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134456777</t>
+          <t>https://artportalen.se/Sighting/134456780</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134456770</v>
+        <v>135333617</v>
       </c>
       <c r="B11" t="n">
-        <v>78377</v>
+        <v>83292</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,21 +1715,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6487</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,13 +1739,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>623875</v>
+        <v>623762</v>
       </c>
       <c r="R11" t="n">
-        <v>7310171</v>
+        <v>7310114</v>
       </c>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1753,22 +1769,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1783,27 +1799,31 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134456770</t>
+          <t>https://artportalen.se/Sighting/135333617</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134456773</v>
+        <v>135333622</v>
       </c>
       <c r="B12" t="n">
-        <v>57975</v>
+        <v>83292</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,21 +1831,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,13 +1855,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>623744</v>
+        <v>623739</v>
       </c>
       <c r="R12" t="n">
-        <v>7310162</v>
+        <v>7310146</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1865,27 +1885,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:20</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack i tall.</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1900,49 +1915,53 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134456773</t>
+          <t>https://artportalen.se/Sighting/135333622</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134456775</v>
+        <v>135330534</v>
       </c>
       <c r="B13" t="n">
-        <v>57975</v>
+        <v>92011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1952,13 +1971,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>623790</v>
+        <v>623725</v>
       </c>
       <c r="R13" t="n">
-        <v>7310142</v>
+        <v>7310245</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1982,27 +2001,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>20:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Gamla hackmärken i tall</t>
+          <t>20:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2017,65 +2031,69 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Petya Valcheva</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134456775</t>
+          <t>https://artportalen.se/Sighting/135330534</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134456766</v>
+        <v>135331260</v>
       </c>
       <c r="B14" t="n">
-        <v>79963</v>
+        <v>79441</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Myrås, Pi lm</t>
+          <t>Myrås, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>623830</v>
+        <v>623814</v>
       </c>
       <c r="R14" t="n">
-        <v>7310041</v>
+        <v>7310091</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2099,22 +2117,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2129,65 +2147,69 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Maja Rancic</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134456766</t>
+          <t>https://artportalen.se/Sighting/135331260</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134456767</v>
+        <v>135331261</v>
       </c>
       <c r="B15" t="n">
-        <v>79963</v>
+        <v>79441</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Myrås, Pi lm</t>
+          <t>Myrås, Pi lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>623900</v>
+        <v>623779</v>
       </c>
       <c r="R15" t="n">
-        <v>7310120</v>
+        <v>7310157</v>
       </c>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2211,22 +2233,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2241,49 +2263,53 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Maja Rancic</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Maja Rancic</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134456767</t>
+          <t>https://artportalen.se/Sighting/135331261</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134456778</v>
+        <v>135333620</v>
       </c>
       <c r="B16" t="n">
-        <v>79396</v>
+        <v>79441</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>260591</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2293,13 +2319,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>623793</v>
+        <v>623771</v>
       </c>
       <c r="R16" t="n">
-        <v>7310206</v>
+        <v>7310137</v>
       </c>
       <c r="S16" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2323,22 +2349,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2353,18 +2379,4889 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333620</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135333618</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>623772</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7310131</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333618</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135333623</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>623707</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7310261</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333623</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135333630</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>623777</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7310269</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333630</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135336952</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>623805</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7310020</v>
+      </c>
+      <c r="S20" t="n">
+        <v>8</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336952</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>134456779</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>623810</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7310162</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
           <t>Sebastian Kirppu</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
+      <c r="AX21" t="inlineStr">
         <is>
           <t>Sebastian Kirppu</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
-      <c r="AZ16" t="inlineStr">
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456779</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135333627</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79198</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>623753</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7310291</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333627</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>134456769</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>623900</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7310143</v>
+      </c>
+      <c r="S23" t="n">
+        <v>14</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456769</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>134456776</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>623807</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7310160</v>
+      </c>
+      <c r="S24" t="n">
+        <v>18</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456776</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>134456777</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>623758</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7310258</v>
+      </c>
+      <c r="S25" t="n">
+        <v>20</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456777</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135330531</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>623713</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7310247</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330531</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135333621</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>623770</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7310168</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333621</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135333625</v>
+      </c>
+      <c r="B28" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>623754</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7310291</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333625</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135333631</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>623776</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7310265</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333631</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135333633</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>623803</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7310251</v>
+      </c>
+      <c r="S30" t="n">
+        <v>20</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333633</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135333636</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>623860</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7310128</v>
+      </c>
+      <c r="S31" t="n">
+        <v>6</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333636</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135336953</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>623790</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7310126</v>
+      </c>
+      <c r="S32" t="n">
+        <v>6</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336953</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135336958</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>623711</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7310252</v>
+      </c>
+      <c r="S33" t="n">
+        <v>8</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336958</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135336963</v>
+      </c>
+      <c r="B34" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>623802</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7310245</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336963</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135358159</v>
+      </c>
+      <c r="B35" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>623777</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7310175</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Maja Rancic</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Maja Rancic</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358159</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>134456770</v>
+      </c>
+      <c r="B36" t="n">
+        <v>78377</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>623875</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7310171</v>
+      </c>
+      <c r="S36" t="n">
+        <v>11</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456770</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135333628</v>
+      </c>
+      <c r="B37" t="n">
+        <v>78445</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>623755</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7310283</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333628</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>134456773</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>623744</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7310162</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack i tall.</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456773</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>134456775</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>623790</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7310142</v>
+      </c>
+      <c r="S39" t="n">
+        <v>20</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Gamla hackmärken i tall</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456775</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135336954</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>623782</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7310156</v>
+      </c>
+      <c r="S40" t="n">
+        <v>7</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336954</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135336955</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>623750</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7310194</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336955</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135336960</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>623741</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7310258</v>
+      </c>
+      <c r="S42" t="n">
+        <v>8</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336960</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135336965</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>623813</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7310236</v>
+      </c>
+      <c r="S43" t="n">
+        <v>6</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336965</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135331264</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98136</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>623755</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7310300</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Maja Rancic</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Maja Rancic</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331264</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135336951</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99296</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>623787</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7310002</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336951</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135330530</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>623714</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7310251</v>
+      </c>
+      <c r="S46" t="n">
+        <v>9</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330530</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135333626</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>623753</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7310291</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333626</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>134456766</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>623830</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7310041</v>
+      </c>
+      <c r="S48" t="n">
+        <v>25</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456766</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>134456767</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>623900</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7310120</v>
+      </c>
+      <c r="S49" t="n">
+        <v>13</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134456767</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>135331263</v>
+      </c>
+      <c r="B50" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>623731</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7310280</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Maja Rancic</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Maja Rancic</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135331263</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>135333624</v>
+      </c>
+      <c r="B51" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>623709</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7310261</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333624</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>135333629</v>
+      </c>
+      <c r="B52" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>623753</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7310283</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135333629</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>135336957</v>
+      </c>
+      <c r="B53" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>623699</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7310215</v>
+      </c>
+      <c r="S53" t="n">
+        <v>8</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336957</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>134456778</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>623793</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7310206</v>
+      </c>
+      <c r="S54" t="n">
+        <v>11</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134456778</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>135330533</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>623740</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7310280</v>
+      </c>
+      <c r="S55" t="n">
+        <v>17</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Petya Valcheva</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330533</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135336956</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>623738</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7310208</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336956</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135336959</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>623723</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7310256</v>
+      </c>
+      <c r="S57" t="n">
+        <v>9</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336959</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>135336964</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Myrås, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>623808</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7310244</v>
+      </c>
+      <c r="S58" t="n">
+        <v>9</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>rikligt med soral</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336964</t>
         </is>
       </c>
     </row>
@@ -2385,6 +7282,48 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 64837-2023 artfynd.xlsx
+++ b/artfynd/A 64837-2023 artfynd.xlsx
@@ -1939,7 +1939,7 @@
         <v>135330534</v>
       </c>
       <c r="B13" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>135331264</v>
       </c>
       <c r="B44" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
         <v>135336951</v>
       </c>
       <c r="B45" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
